--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-15).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-15).xlsx
@@ -938,16 +938,16 @@
     <t>32</t>
   </si>
   <si>
-    <t>R$ 5.312,32</t>
-  </si>
-  <si>
-    <t>55.4</t>
+    <t>R$ 5.323,49</t>
+  </si>
+  <si>
+    <t>55.5</t>
   </si>
   <si>
     <t>33.7</t>
   </si>
   <si>
-    <t>5.49</t>
+    <t>5.50</t>
   </si>
   <si>
     <t>19.4</t>
@@ -7664,7 +7664,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7694,14 +7694,26 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
+      <c r="M42" s="5">
+        <v>4787.1300000000001</v>
+      </c>
+      <c r="N42" s="6">
+        <v>49</v>
+      </c>
       <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
+      <c r="P42" s="7">
+        <v>7.0221081632653064</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>25.049075000000002</v>
+      </c>
+      <c r="R42" s="8">
+        <v>11.97258064516129</v>
+      </c>
       <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
+      <c r="T42" s="9">
+        <v>0.27777777777777779</v>
+      </c>
       <c r="U42" s="9"/>
       <c r="V42" s="9"/>
       <c r="W42" s="9"/>
@@ -24510,7 +24522,7 @@
         <v>19847</v>
       </c>
       <c r="B156" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>51</v>
@@ -24540,30 +24552,18 @@
         <v>58</v>
       </c>
       <c r="L156" s="4"/>
-      <c r="M156" s="5">
-        <v>2752.9000000000001</v>
-      </c>
-      <c r="N156" s="6">
-        <v>27</v>
-      </c>
+      <c r="M156" s="5"/>
+      <c r="N156" s="6"/>
       <c r="O156" s="6">
         <v>22</v>
       </c>
-      <c r="P156" s="7">
-        <v>6.5326923076923071</v>
-      </c>
-      <c r="Q156" s="8">
-        <v>17.828786363636365</v>
-      </c>
-      <c r="R156" s="8">
-        <v>4.1886363636363635</v>
-      </c>
+      <c r="P156" s="7"/>
+      <c r="Q156" s="8"/>
+      <c r="R156" s="8"/>
       <c r="S156" s="8">
         <v>7</v>
       </c>
-      <c r="T156" s="9">
-        <v>0.27272727272727271</v>
-      </c>
+      <c r="T156" s="9"/>
       <c r="U156" s="9">
         <v>0.22727272727272727</v>
       </c>

--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-15).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-15).xlsx
@@ -935,37 +935,37 @@
     <t>214</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 5.323,49</t>
-  </si>
-  <si>
-    <t>55.5</t>
-  </si>
-  <si>
-    <t>33.7</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 5.288,02</t>
+  </si>
+  <si>
+    <t>55.3</t>
+  </si>
+  <si>
+    <t>33.5</t>
   </si>
   <si>
     <t>5.50</t>
   </si>
   <si>
-    <t>19.4</t>
+    <t>19.3</t>
   </si>
   <si>
     <t>7.3</t>
   </si>
   <si>
-    <t>6.0</t>
+    <t>6.1</t>
   </si>
   <si>
     <t>38.7%</t>
   </si>
   <si>
-    <t>17.1%</t>
-  </si>
-  <si>
-    <t>2.0%</t>
+    <t>17.2%</t>
+  </si>
+  <si>
+    <t>1.9%</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -980,43 +980,43 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.9%</t>
+    <t>6.0%</t>
   </si>
   <si>
     <t>2.7%</t>
   </si>
   <si>
-    <t>4.4%</t>
-  </si>
-  <si>
-    <t>1252.0</t>
-  </si>
-  <si>
-    <t>1020.0</t>
+    <t>4.6%</t>
+  </si>
+  <si>
+    <t>1277.0</t>
+  </si>
+  <si>
+    <t>1038.0</t>
   </si>
   <si>
     <t>117.0</t>
   </si>
   <si>
-    <t>31.0</t>
-  </si>
-  <si>
-    <t>238.0</t>
-  </si>
-  <si>
-    <t>79.0</t>
+    <t>32.0</t>
+  </si>
+  <si>
+    <t>241.0</t>
+  </si>
+  <si>
+    <t>81.0</t>
   </si>
   <si>
     <t>11.0</t>
   </si>
   <si>
-    <t>354.0</t>
-  </si>
-  <si>
-    <t>160.0</t>
-  </si>
-  <si>
-    <t>264.0</t>
+    <t>361.0</t>
+  </si>
+  <si>
+    <t>161.0</t>
+  </si>
+  <si>
+    <t>276.0</t>
   </si>
   <si>
     <t>29.0</t>
@@ -7700,7 +7700,9 @@
       <c r="N42" s="6">
         <v>49</v>
       </c>
-      <c r="O42" s="6"/>
+      <c r="O42" s="6">
+        <v>36</v>
+      </c>
       <c r="P42" s="7">
         <v>7.0221081632653064</v>
       </c>
@@ -7710,31 +7712,75 @@
       <c r="R42" s="8">
         <v>11.97258064516129</v>
       </c>
-      <c r="S42" s="8"/>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
       <c r="T42" s="9">
         <v>0.27777777777777779</v>
       </c>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="U42" s="9">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -12690,7 +12736,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12718,14 +12764,26 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
+      <c r="M76" s="5">
+        <v>5519.0799999999999</v>
+      </c>
+      <c r="N76" s="6">
+        <v>69</v>
+      </c>
       <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
+      <c r="P76" s="7">
+        <v>5.7915492957746482</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>19</v>
+      </c>
+      <c r="R76" s="8">
+        <v>5.9434782608695649</v>
+      </c>
       <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
+      <c r="T76" s="9">
+        <v>0.37931034482758619</v>
+      </c>
       <c r="U76" s="9"/>
       <c r="V76" s="9"/>
       <c r="W76" s="9"/>
@@ -16518,7 +16576,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16548,35 +16606,91 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
+      <c r="M102" s="5">
+        <v>1819.45</v>
+      </c>
+      <c r="N102" s="6">
+        <v>19</v>
+      </c>
+      <c r="O102" s="6">
+        <v>15</v>
+      </c>
+      <c r="P102" s="7">
+        <v>4.1341650000000003</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>1</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.066666666666000005</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -17789,7 +17903,9 @@
       <c r="N111" s="6">
         <v>7</v>
       </c>
-      <c r="O111" s="6"/>
+      <c r="O111" s="6">
+        <v>6</v>
+      </c>
       <c r="P111" s="7">
         <v>4.8645874999999998</v>
       </c>
@@ -17799,31 +17915,75 @@
       <c r="R111" s="8">
         <v>0.97778333333333334</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
       <c r="T111" s="9">
         <v>0.66666666666666663</v>
       </c>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="U111" s="9">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>
@@ -24522,7 +24682,7 @@
         <v>19847</v>
       </c>
       <c r="B156" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>51</v>
@@ -24552,18 +24712,30 @@
         <v>58</v>
       </c>
       <c r="L156" s="4"/>
-      <c r="M156" s="5"/>
-      <c r="N156" s="6"/>
+      <c r="M156" s="5">
+        <v>2752.9000000000001</v>
+      </c>
+      <c r="N156" s="6">
+        <v>27</v>
+      </c>
       <c r="O156" s="6">
         <v>22</v>
       </c>
-      <c r="P156" s="7"/>
-      <c r="Q156" s="8"/>
-      <c r="R156" s="8"/>
+      <c r="P156" s="7">
+        <v>6.5326923076923071</v>
+      </c>
+      <c r="Q156" s="8">
+        <v>17.828786363636365</v>
+      </c>
+      <c r="R156" s="8">
+        <v>4.1886363636363635</v>
+      </c>
       <c r="S156" s="8">
         <v>7</v>
       </c>
-      <c r="T156" s="9"/>
+      <c r="T156" s="9">
+        <v>0.27272727272727271</v>
+      </c>
       <c r="U156" s="9">
         <v>0.22727272727272727</v>
       </c>
@@ -30235,7 +30407,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -30265,14 +30437,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>4604.2700000000004</v>
+      </c>
+      <c r="N195" s="6">
+        <v>56</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>6.949320408163266</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>19.720834374999999</v>
+      </c>
+      <c r="R195" s="8">
+        <v>5.5406250000000004</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.15625</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>

--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-15).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-15).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 5.288,02</t>
-  </si>
-  <si>
-    <t>55.3</t>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 5.296,19</t>
+  </si>
+  <si>
+    <t>55.4</t>
   </si>
   <si>
     <t>33.5</t>
   </si>
   <si>
-    <t>5.50</t>
+    <t>5.49</t>
   </si>
   <si>
     <t>19.3</t>
@@ -956,16 +956,16 @@
     <t>7.3</t>
   </si>
   <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>38.7%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>38.6%</t>
   </si>
   <si>
     <t>17.2%</t>
   </si>
   <si>
-    <t>1.9%</t>
+    <t>2.0%</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -983,43 +983,43 @@
     <t>6.0%</t>
   </si>
   <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>4.6%</t>
-  </si>
-  <si>
-    <t>1277.0</t>
-  </si>
-  <si>
-    <t>1038.0</t>
-  </si>
-  <si>
-    <t>117.0</t>
+    <t>2.6%</t>
+  </si>
+  <si>
+    <t>4.5%</t>
+  </si>
+  <si>
+    <t>1297.0</t>
+  </si>
+  <si>
+    <t>1054.0</t>
+  </si>
+  <si>
+    <t>120.0</t>
   </si>
   <si>
     <t>32.0</t>
   </si>
   <si>
-    <t>241.0</t>
-  </si>
-  <si>
-    <t>81.0</t>
+    <t>244.0</t>
+  </si>
+  <si>
+    <t>82.0</t>
   </si>
   <si>
     <t>11.0</t>
   </si>
   <si>
-    <t>361.0</t>
-  </si>
-  <si>
-    <t>161.0</t>
-  </si>
-  <si>
-    <t>276.0</t>
-  </si>
-  <si>
-    <t>29.0</t>
+    <t>369.0</t>
+  </si>
+  <si>
+    <t>162.0</t>
+  </si>
+  <si>
+    <t>279.0</t>
+  </si>
+  <si>
+    <t>30.0</t>
   </si>
   <si>
     <t>1</t>
@@ -10102,7 +10102,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10132,35 +10132,93 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
-      <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="M58" s="5">
+        <v>6814.8500000000004</v>
+      </c>
+      <c r="N58" s="6">
+        <v>77</v>
+      </c>
+      <c r="O58" s="6">
+        <v>53</v>
+      </c>
+      <c r="P58" s="7">
+        <v>3.4972217948717947</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>15.774843396226414</v>
+      </c>
+      <c r="R58" s="8">
+        <v>5.2808169811320758</v>
+      </c>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
+      <c r="T58" s="9">
+        <v>0.56603773584905659</v>
+      </c>
+      <c r="U58" s="9">
+        <v>0.094339622641509441</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.056603773584905662</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -12770,7 +12828,9 @@
       <c r="N76" s="6">
         <v>69</v>
       </c>
-      <c r="O76" s="6"/>
+      <c r="O76" s="6">
+        <v>29</v>
+      </c>
       <c r="P76" s="7">
         <v>5.7915492957746482</v>
       </c>
@@ -12780,31 +12840,75 @@
       <c r="R76" s="8">
         <v>5.9434782608695649</v>
       </c>
-      <c r="S76" s="8"/>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
       <c r="T76" s="9">
         <v>0.37931034482758619</v>
       </c>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="U76" s="9">
+        <v>0.37931034482758619</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.10344827586206896</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -28091,7 +28195,9 @@
       <c r="N179" s="6">
         <v>57</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>24</v>
+      </c>
       <c r="P179" s="7">
         <v>4.077878181818182</v>
       </c>
@@ -28101,31 +28207,75 @@
       <c r="R179" s="8">
         <v>2.0277791666666665</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.83333333333333337</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
